--- a/ig/nr-change-signes-vitaux-display/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr-change-signes-vitaux-display/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4033" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="680">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:47:58+00:00</t>
+    <t>2023-11-28T12:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,11 +440,10 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.</t>
-  </si>
-  <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -1734,9 +1733,6 @@
   </si>
   <si>
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J158-MethodStepsByDay-ENS/FHIR/JDV-J158-MethodStepsByDay-ENS</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J146-MethodBodyHeight-ENS/FHIR/JDV-J146-MethodBodyHeight-ENS</t>
@@ -12191,7 +12187,7 @@
         <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>80</v>
@@ -12237,13 +12233,11 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y81" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y81" s="2"/>
+      <c r="Z81" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12282,10 +12276,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12296,10 +12290,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12322,16 +12316,16 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12381,7 +12375,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12399,27 +12393,27 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12442,16 +12436,16 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12501,7 +12495,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12519,27 +12513,27 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>574</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12562,19 +12556,19 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12623,7 +12617,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12635,19 +12629,19 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12658,10 +12652,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12776,10 +12770,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12896,14 +12890,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12925,10 +12919,10 @@
         <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>117</v>
@@ -12983,7 +12977,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13018,10 +13012,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13044,16 +13038,16 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13103,7 +13097,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13112,22 +13106,22 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ88" t="s" s="2">
+      <c r="AK88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13138,10 +13132,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13164,16 +13158,16 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="N89" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13223,7 +13217,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13232,22 +13226,22 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ89" t="s" s="2">
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AK89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AN89" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13258,10 +13252,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13287,16 +13281,16 @@
         <v>254</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13324,11 +13318,11 @@
         <v>175</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13345,7 +13339,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13363,10 +13357,10 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>528</v>
@@ -13380,10 +13374,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13409,16 +13403,16 @@
         <v>254</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13446,11 +13440,11 @@
         <v>161</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13467,7 +13461,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13485,10 +13479,10 @@
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>528</v>
@@ -13502,10 +13496,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13528,19 +13522,19 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13589,7 +13583,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13601,19 +13595,19 @@
         <v>103</v>
       </c>
       <c r="AJ92" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AK92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13624,10 +13618,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13653,10 +13647,10 @@
         <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>306</v>
@@ -13709,7 +13703,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13730,10 +13724,10 @@
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13744,10 +13738,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13770,16 +13764,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13829,7 +13823,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13850,10 +13844,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13864,10 +13858,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13890,16 +13884,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13949,7 +13943,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13970,10 +13964,10 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13984,10 +13978,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14010,19 +14004,19 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14071,7 +14065,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14083,19 +14077,19 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AK96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14106,10 +14100,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14224,10 +14218,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14344,14 +14338,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14373,10 +14367,10 @@
         <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>117</v>
@@ -14431,7 +14425,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14466,10 +14460,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14495,16 +14489,16 @@
         <v>254</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14553,7 +14547,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -14571,7 +14565,7 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>349</v>
@@ -14588,10 +14582,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14614,16 +14608,16 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>436</v>
@@ -14654,11 +14648,11 @@
         <v>245</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>668</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14675,7 +14669,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14684,7 +14678,7 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>104</v>
@@ -14693,7 +14687,7 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>441</v>
@@ -14710,10 +14704,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14739,13 +14733,13 @@
         <v>254</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>503</v>
@@ -14797,7 +14791,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14806,7 +14800,7 @@
         <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>104</v>
@@ -14832,10 +14826,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14898,7 +14892,7 @@
         <v>151</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Z103" t="s" s="2">
         <v>525</v>
@@ -14919,7 +14913,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14954,10 +14948,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14983,16 +14977,16 @@
         <v>81</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>680</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15041,7 +15035,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15062,10 +15056,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
